--- a/Section 4.3/D_metrics_vs_load_m0.001_PV75.0_gr3.0.xlsx
+++ b/Section 4.3/D_metrics_vs_load_m0.001_PV75.0_gr3.0.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Reworked_TEA\nj=1,bj0.0005\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B7CC716-0C4E-40D2-898E-167FAD74EEC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120"/>
   </bookViews>
   <sheets>
-    <sheet name="data" sheetId="2" r:id="rId3"/>
+    <sheet name="data" sheetId="2" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="125725" fullCalcOnLoad="true"/>
+  <calcPr calcId="191029" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="14" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="42" uniqueCount="7">
   <si>
     <t>min_load</t>
   </si>
@@ -75,13 +81,338 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="true">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="false"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="true">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="false"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="true">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="false"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="true"/>
     <col min="2" max="2" width="11.7109375" customWidth="true"/>
@@ -92,7 +423,7 @@
     <col min="7" max="7" width="11.7109375" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
       <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
@@ -115,305 +446,352 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
       <c r="A2" s="0">
-        <v>7.7999999999999998</v>
+        <v>6.5</v>
       </c>
       <c r="B2" s="0">
-        <v>32.81762867590961</v>
+        <v>20.76841186545234</v>
       </c>
       <c r="C2" s="0">
-        <v>71.787346941142431</v>
+        <v>43.128908710413185</v>
       </c>
       <c r="D2" s="0">
-        <v>9.3573529167512977</v>
+        <v>7.8868377034096122</v>
       </c>
       <c r="E2" s="0">
-        <v>56.392655356997928</v>
+        <v>55.878069209640415</v>
       </c>
       <c r="F2" s="0">
-        <v>64.399988828863826</v>
+        <v>64.084645554664419</v>
       </c>
       <c r="G2" s="0">
-        <v>8.5884539719136459</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>8.5357384875367845</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
       <c r="A3" s="0">
         <v>8</v>
       </c>
       <c r="B3" s="0">
-        <v>41.779821073722495</v>
+        <v>41.77662465016337</v>
       </c>
       <c r="C3" s="0">
-        <v>87.127724510716092</v>
+        <v>79.292625459816037</v>
       </c>
       <c r="D3" s="0">
-        <v>11.965600588643358</v>
+        <v>20.271013799003505</v>
       </c>
       <c r="E3" s="0">
-        <v>56.725883097092542</v>
+        <v>56.741774016563795</v>
       </c>
       <c r="F3" s="0">
-        <v>64.206453741293942</v>
+        <v>64.103632406460903</v>
       </c>
       <c r="G3" s="0">
-        <v>8.4322045062976603</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>8.0875718170153288</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
       <c r="A4" s="0">
         <v>10</v>
       </c>
       <c r="B4" s="0">
-        <v>41.515413257872872</v>
+        <v>39.956785080931866</v>
       </c>
       <c r="C4" s="0">
-        <v>85.254647128253382</v>
+        <v>71.906863289531614</v>
       </c>
       <c r="D4" s="0">
-        <v>11.263886101685394</v>
+        <v>13.815003031316381</v>
       </c>
       <c r="E4" s="0">
-        <v>56.544808214830297</v>
+        <v>56.619076081226773</v>
       </c>
       <c r="F4" s="0">
-        <v>64.044162494708786</v>
+        <v>63.968176744219861</v>
       </c>
       <c r="G4" s="0">
-        <v>8.4328396100053098</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>8.1246041713246093</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
       <c r="A5" s="0">
         <v>11</v>
       </c>
       <c r="B5" s="0">
-        <v>42.930219134919163</v>
+        <v>40.394868882280406</v>
       </c>
       <c r="C5" s="0">
-        <v>88.164820199478854</v>
+        <v>71.938341766127493</v>
       </c>
       <c r="D5" s="0">
-        <v>14.09772240278383</v>
+        <v>13.359169078902845</v>
       </c>
       <c r="E5" s="0">
-        <v>56.517672224619453</v>
+        <v>56.533585906913096</v>
       </c>
       <c r="F5" s="0">
-        <v>63.822407960204785</v>
+        <v>63.869392379190899</v>
       </c>
       <c r="G5" s="0">
-        <v>8.4231010587152095</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>8.1184077283416975</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
       <c r="A6" s="0">
         <v>13</v>
       </c>
       <c r="B6" s="0">
-        <v>42.404202963296285</v>
+        <v>42.763295752081333</v>
       </c>
       <c r="C6" s="0">
-        <v>84.95100168676187</v>
+        <v>75.699985165358555</v>
       </c>
       <c r="D6" s="0">
-        <v>14.559590347579912</v>
+        <v>14.131576295092898</v>
       </c>
       <c r="E6" s="0">
-        <v>56.438184530163831</v>
+        <v>56.359226995519222</v>
       </c>
       <c r="F6" s="0">
-        <v>63.690998208493156</v>
+        <v>63.982364498048526</v>
       </c>
       <c r="G6" s="0">
-        <v>8.4295725479133399</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>8.0722354559297198</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
       <c r="A7" s="0">
         <v>15</v>
       </c>
       <c r="B7" s="0">
-        <v>42.518787311617842</v>
+        <v>40.381549997913062</v>
       </c>
       <c r="C7" s="0">
-        <v>85.039994862357005</v>
+        <v>70.21724958001306</v>
       </c>
       <c r="D7" s="0">
-        <v>15.082247722028916</v>
+        <v>19.372556111146295</v>
       </c>
       <c r="E7" s="0">
-        <v>56.282319651353021</v>
+        <v>56.423910917776823</v>
       </c>
       <c r="F7" s="0">
-        <v>63.520510293242289</v>
+        <v>63.781148203398288</v>
       </c>
       <c r="G7" s="0">
-        <v>8.4282860250742075</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>8.1088680742352057</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
       <c r="A8" s="0">
         <v>18</v>
       </c>
       <c r="B8" s="0">
-        <v>41.849171290710565</v>
+        <v>42.187351739409699</v>
       </c>
       <c r="C8" s="0">
-        <v>82.484037279936288</v>
+        <v>72.035622383144286</v>
       </c>
       <c r="D8" s="0">
-        <v>13.294146534616688</v>
+        <v>18.960110969489076</v>
       </c>
       <c r="E8" s="0">
-        <v>55.940133107125632</v>
+        <v>56.111523999224957</v>
       </c>
       <c r="F8" s="0">
-        <v>63.566488942547466</v>
+        <v>63.607778565793573</v>
       </c>
       <c r="G8" s="0">
-        <v>8.42894955650989</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>8.0838506852190566</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
       <c r="A9" s="0">
         <v>20</v>
       </c>
       <c r="B9" s="0">
-        <v>42.341495231788784</v>
+        <v>42.949533665844953</v>
       </c>
       <c r="C9" s="0">
-        <v>83.839299671038432</v>
+        <v>73.338101054583149</v>
       </c>
       <c r="D9" s="0">
-        <v>16.232938229895115</v>
+        <v>19.027999189374189</v>
       </c>
       <c r="E9" s="0">
-        <v>55.862800513032902</v>
+        <v>55.873984063761831</v>
       </c>
       <c r="F9" s="0">
-        <v>63.276745793958142</v>
+        <v>63.642033304472875</v>
       </c>
       <c r="G9" s="0">
-        <v>8.4280722948516669</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>8.0702484716917926</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
       <c r="A10" s="0">
         <v>22</v>
       </c>
       <c r="B10" s="0">
-        <v>42.116541670182016</v>
+        <v>41.602983106464677</v>
       </c>
       <c r="C10" s="0">
-        <v>83.6964996524935</v>
+        <v>70.767729627471965</v>
       </c>
       <c r="D10" s="0">
-        <v>16.491284670577024</v>
+        <v>19.542911076874724</v>
       </c>
       <c r="E10" s="0">
-        <v>55.68764154549644</v>
+        <v>55.728277071716931</v>
       </c>
       <c r="F10" s="0">
-        <v>63.192117902240398</v>
+        <v>63.381083744224505</v>
       </c>
       <c r="G10" s="0">
-        <v>8.4297436341279166</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>8.0917314206669975</v>
+      </c>
+      <c r="N10">
+        <v>28.000000000000004</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
       <c r="A11" s="0">
         <v>25</v>
       </c>
       <c r="B11" s="0">
-        <v>40.974613095006319</v>
+        <v>40.880566720931512</v>
       </c>
       <c r="C11" s="0">
-        <v>80.38332576947667</v>
+        <v>69.181881056972102</v>
       </c>
       <c r="D11" s="0">
-        <v>14.496846922983805</v>
+        <v>22.841140327735669</v>
       </c>
       <c r="E11" s="0">
-        <v>55.301870782202037</v>
+        <v>55.483381736252547</v>
       </c>
       <c r="F11" s="0">
-        <v>63.317511435857256</v>
+        <v>63.231008136258467</v>
       </c>
       <c r="G11" s="0">
-        <v>8.4388481728854643</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>8.0994755519494639</v>
+      </c>
+      <c r="N11">
+        <v>41.122966465627229</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
       <c r="A12" s="0">
         <v>28.000000000000004</v>
       </c>
       <c r="B12" s="0">
-        <v>40.602228132824393</v>
+        <v>41.122966465627229</v>
       </c>
       <c r="C12" s="0">
-        <v>79.78303382365317</v>
+        <v>69.133432662438651</v>
       </c>
       <c r="D12" s="0">
-        <v>14.255123659753391</v>
+        <v>21.321849687483891</v>
       </c>
       <c r="E12" s="0">
-        <v>54.926733575065043</v>
+        <v>55.10120549859289</v>
       </c>
       <c r="F12" s="0">
-        <v>63.182374714114161</v>
+        <v>63.117833253069094</v>
       </c>
       <c r="G12" s="0">
-        <v>8.4419744337018052</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>8.0956615639919498</v>
+      </c>
+      <c r="N12">
+        <v>69.133432662438651</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
       <c r="A13" s="0">
         <v>30</v>
       </c>
       <c r="B13" s="0">
-        <v>40.205024198257163</v>
+        <v>41.246366847251878</v>
       </c>
       <c r="C13" s="0">
-        <v>79.495743042033226</v>
+        <v>69.317618801070807</v>
       </c>
       <c r="D13" s="0">
-        <v>14.250015820908457</v>
+        <v>20.330912589571312</v>
       </c>
       <c r="E13" s="0">
-        <v>54.602155655033485</v>
+        <v>54.766111238227516</v>
       </c>
       <c r="F13" s="0">
-        <v>63.107520294858389</v>
+        <v>63.18111795262697</v>
       </c>
       <c r="G13" s="0">
-        <v>8.4456542872194031</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>8.0899371294371392</v>
+      </c>
+      <c r="N13">
+        <v>21.321849687483891</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.25">
       <c r="A14" s="0">
         <v>35</v>
       </c>
       <c r="B14" s="0">
-        <v>38.949164358549254</v>
+        <v>40.058600053737329</v>
       </c>
       <c r="C14" s="0">
-        <v>78.297563524225069</v>
+        <v>67.78979960255748</v>
       </c>
       <c r="D14" s="0">
-        <v>13.965210222499568</v>
+        <v>18.999031881020695</v>
       </c>
       <c r="E14" s="0">
-        <v>53.658278225870696</v>
+        <v>53.777730931672288</v>
       </c>
       <c r="F14" s="0">
-        <v>62.961766896922455</v>
+        <v>63.098779491957089</v>
       </c>
       <c r="G14" s="0">
-        <v>8.4582674152511679</v>
+        <v>8.0994171611741184</v>
+      </c>
+      <c r="N14">
+        <v>55.10120549859289</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
+      <c r="A15" s="0">
+        <v>40</v>
+      </c>
+      <c r="B15" s="0">
+        <v>38.089252133306843</v>
+      </c>
+      <c r="C15" s="0">
+        <v>65.182661938112972</v>
+      </c>
+      <c r="D15" s="0">
+        <v>16.315517211211517</v>
+      </c>
+      <c r="E15" s="0">
+        <v>52.631375279569916</v>
+      </c>
+      <c r="F15" s="0">
+        <v>63.07398814000674</v>
+      </c>
+      <c r="G15" s="0">
+        <v>8.1158073368102368</v>
+      </c>
+      <c r="N15">
+        <v>63.117833253069094</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.25">
+      <c r="N16">
+        <v>8.0956615639919498</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>